--- a/Pruebas calificadas/COLEGIO JUAN REY_901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JUAN REY_901_CALIFICADO.xlsx
@@ -3215,9 +3215,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -3721,9 +3721,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -9789,9 +9789,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB37" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -10793,9 +10793,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB41" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -11805,9 +11805,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB45" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -12813,9 +12813,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB49" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -13319,9 +13319,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB51" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -13825,9 +13825,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB53" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -14331,9 +14331,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB55" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -14829,9 +14829,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB57" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO JUAN REY_901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JUAN REY_901_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,11 +6036,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6132,7 +6044,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,11 +6285,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6385,7 +6293,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,11 +6534,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6638,7 +6542,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6879,11 +6783,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -6891,7 +6791,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7132,11 +7032,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -7144,7 +7040,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7385,11 +7281,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -7397,7 +7289,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7638,11 +7530,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -7650,7 +7538,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7891,11 +7779,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -7903,7 +7787,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8144,11 +8028,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8156,7 +8036,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8397,11 +8277,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8409,7 +8285,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8650,11 +8526,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8662,7 +8534,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8903,11 +8775,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -8915,7 +8783,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9156,11 +9024,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9168,7 +9032,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9409,11 +9273,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9421,7 +9281,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9670,7 +9526,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -9923,7 +9775,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10176,7 +10024,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10417,11 +10265,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10429,7 +10273,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10670,11 +10514,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10682,7 +10522,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10915,11 +10755,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -10927,7 +10763,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11168,11 +11004,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11180,7 +11012,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11421,11 +11253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11433,7 +11261,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11674,11 +11502,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11686,7 +11510,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11927,11 +11751,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -11939,7 +11759,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12180,11 +12000,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12192,7 +12008,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12433,11 +12249,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12445,7 +12257,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12682,11 +12494,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12694,7 +12502,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12935,11 +12743,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -12947,7 +12751,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13188,11 +12992,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -13200,7 +13000,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13441,11 +13241,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -13453,7 +13249,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13694,11 +13490,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -13706,7 +13498,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13947,11 +13739,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -13959,7 +13747,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14200,11 +13988,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -14212,7 +13996,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14453,11 +14237,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -14465,7 +14245,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14702,11 +14482,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -14714,7 +14490,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14947,11 +14723,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -14959,7 +14731,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15200,11 +14972,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -15212,7 +14980,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15453,11 +15221,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -15465,7 +15229,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15706,11 +15470,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001034011</t>
@@ -15718,7 +15478,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JUAN REY (IED)</t>
+          <t>COLEGIO JUAN REY</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
